--- a/MainTop/28.05.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/28.05.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\28.05.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358BCE5C-7370-49EC-82D3-5B85616DB5DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7002FD7-00AE-4115-BC2F-B212E769AD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -729,10 +729,9 @@
   <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="48.7109375" customWidth="1"/>
+    <col min="1" max="1" width="52.140625" customWidth="1"/>
     <col min="2" max="5" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" customWidth="1"/>
-    <col min="7" max="7" width="7" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
@@ -778,7 +777,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>9</v>
@@ -882,7 +881,7 @@
         <v>23</v>
       </c>
       <c r="F6" s="2">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>9</v>

--- a/MainTop/28.05.2026 Макс ВБ/print_print_sorted.xlsx
+++ b/MainTop/28.05.2026 Макс ВБ/print_print_sorted.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\28.05.2026 Макс ВБ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7002FD7-00AE-4115-BC2F-B212E769AD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38AF9017-849D-4553-A341-0FF403E54BB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -414,7 +414,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -424,6 +424,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -726,15 +727,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.140625" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" customWidth="1"/>
     <col min="2" max="5" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" customWidth="1"/>
+    <col min="7" max="7" width="5.7109375" customWidth="1"/>
+    <col min="8" max="8" width="18.42578125" customWidth="1"/>
+    <col min="9" max="9" width="5.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -759,8 +763,9 @@
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I1" s="7"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>8</v>
       </c>
@@ -785,8 +790,12 @@
       <c r="H2" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="7">
+        <f>F2/4</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -811,8 +820,12 @@
       <c r="H3" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="7">
+        <f t="shared" ref="I3:I66" si="0">F3/4</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>12</v>
       </c>
@@ -837,8 +850,12 @@
       <c r="H4" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="7">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
@@ -863,8 +880,12 @@
       <c r="H5" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I5" s="7">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -889,8 +910,12 @@
       <c r="H6" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="7">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>15</v>
       </c>
@@ -915,8 +940,12 @@
       <c r="H7" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>16</v>
       </c>
@@ -941,8 +970,12 @@
       <c r="H8" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>17</v>
       </c>
@@ -967,8 +1000,12 @@
       <c r="H9" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I9" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
@@ -993,8 +1030,12 @@
       <c r="H10" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>19</v>
       </c>
@@ -1019,8 +1060,12 @@
       <c r="H11" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>20</v>
       </c>
@@ -1045,8 +1090,12 @@
       <c r="H12" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I12" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>21</v>
       </c>
@@ -1071,8 +1120,12 @@
       <c r="H13" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>22</v>
       </c>
@@ -1097,8 +1150,12 @@
       <c r="H14" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>23</v>
       </c>
@@ -1123,8 +1180,12 @@
       <c r="H15" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>24</v>
       </c>
@@ -1149,8 +1210,12 @@
       <c r="H16" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I16" s="7">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>25</v>
       </c>
@@ -1175,8 +1240,12 @@
       <c r="H17" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>26</v>
       </c>
@@ -1201,8 +1270,12 @@
       <c r="H18" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>27</v>
       </c>
@@ -1227,8 +1300,12 @@
       <c r="H19" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I19" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>28</v>
       </c>
@@ -1253,8 +1330,12 @@
       <c r="H20" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>29</v>
       </c>
@@ -1279,8 +1360,12 @@
       <c r="H21" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>30</v>
       </c>
@@ -1305,8 +1390,12 @@
       <c r="H22" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>31</v>
       </c>
@@ -1331,8 +1420,12 @@
       <c r="H23" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I23" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>32</v>
       </c>
@@ -1357,8 +1450,12 @@
       <c r="H24" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>33</v>
       </c>
@@ -1383,8 +1480,12 @@
       <c r="H25" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>34</v>
       </c>
@@ -1409,8 +1510,12 @@
       <c r="H26" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I26" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>35</v>
       </c>
@@ -1435,8 +1540,12 @@
       <c r="H27" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>36</v>
       </c>
@@ -1461,8 +1570,12 @@
       <c r="H28" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>37</v>
       </c>
@@ -1487,8 +1600,12 @@
       <c r="H29" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>38</v>
       </c>
@@ -1513,8 +1630,12 @@
       <c r="H30" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>39</v>
       </c>
@@ -1539,8 +1660,12 @@
       <c r="H31" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>40</v>
       </c>
@@ -1565,8 +1690,12 @@
       <c r="H32" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="7">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>41</v>
       </c>
@@ -1591,8 +1720,12 @@
       <c r="H33" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
         <v>42</v>
       </c>
@@ -1617,8 +1750,12 @@
       <c r="H34" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>43</v>
       </c>
@@ -1643,8 +1780,12 @@
       <c r="H35" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>44</v>
       </c>
@@ -1669,8 +1810,12 @@
       <c r="H36" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I36" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
         <v>45</v>
       </c>
@@ -1695,8 +1840,12 @@
       <c r="H37" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I37" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
         <v>46</v>
       </c>
@@ -1721,8 +1870,12 @@
       <c r="H38" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I38" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>47</v>
       </c>
@@ -1747,8 +1900,12 @@
       <c r="H39" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I39" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>48</v>
       </c>
@@ -1773,8 +1930,12 @@
       <c r="H40" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I40" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
         <v>49</v>
       </c>
@@ -1799,8 +1960,12 @@
       <c r="H41" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I41" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>50</v>
       </c>
@@ -1825,8 +1990,12 @@
       <c r="H42" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I42" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
         <v>51</v>
       </c>
@@ -1851,8 +2020,12 @@
       <c r="H43" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I43" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
         <v>52</v>
       </c>
@@ -1877,8 +2050,12 @@
       <c r="H44" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I44" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
         <v>53</v>
       </c>
@@ -1903,8 +2080,12 @@
       <c r="H45" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I45" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>54</v>
       </c>
@@ -1929,8 +2110,12 @@
       <c r="H46" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I46" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>55</v>
       </c>
@@ -1955,8 +2140,12 @@
       <c r="H47" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I47" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>56</v>
       </c>
@@ -1981,8 +2170,12 @@
       <c r="H48" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I48" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
         <v>57</v>
       </c>
@@ -2007,8 +2200,12 @@
       <c r="H49" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I49" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>58</v>
       </c>
@@ -2033,8 +2230,12 @@
       <c r="H50" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I50" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>59</v>
       </c>
@@ -2059,8 +2260,12 @@
       <c r="H51" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I51" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>60</v>
       </c>
@@ -2085,8 +2290,12 @@
       <c r="H52" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I52" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>61</v>
       </c>
@@ -2111,8 +2320,12 @@
       <c r="H53" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I53" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>62</v>
       </c>
@@ -2137,8 +2350,12 @@
       <c r="H54" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I54" s="7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>63</v>
       </c>
@@ -2163,8 +2380,12 @@
       <c r="H55" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I55" s="7">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>65</v>
       </c>
@@ -2189,8 +2410,12 @@
       <c r="H56" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I56" s="7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
         <v>66</v>
       </c>
@@ -2215,8 +2440,12 @@
       <c r="H57" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I57" s="7">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
         <v>67</v>
       </c>
@@ -2241,8 +2470,12 @@
       <c r="H58" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I58" s="7">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
         <v>68</v>
       </c>
@@ -2267,8 +2500,12 @@
       <c r="H59" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I59" s="7">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
         <v>69</v>
       </c>
@@ -2293,8 +2530,12 @@
       <c r="H60" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I60" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
         <v>70</v>
       </c>
@@ -2319,8 +2560,12 @@
       <c r="H61" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I61" s="7">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
         <v>71</v>
       </c>
@@ -2345,8 +2590,12 @@
       <c r="H62" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I62" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
         <v>72</v>
       </c>
@@ -2371,8 +2620,12 @@
       <c r="H63" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I63" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
         <v>73</v>
       </c>
@@ -2397,8 +2650,12 @@
       <c r="H64" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I64" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
         <v>74</v>
       </c>
@@ -2423,8 +2680,12 @@
       <c r="H65" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I65" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
         <v>75</v>
       </c>
@@ -2449,8 +2710,12 @@
       <c r="H66" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I66" s="7">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
         <v>76</v>
       </c>
@@ -2475,8 +2740,12 @@
       <c r="H67" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I67" s="7">
+        <f t="shared" ref="I67:I91" si="1">F67/4</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
         <v>77</v>
       </c>
@@ -2501,8 +2770,12 @@
       <c r="H68" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I68" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
         <v>78</v>
       </c>
@@ -2527,8 +2800,12 @@
       <c r="H69" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I69" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
         <v>79</v>
       </c>
@@ -2553,8 +2830,12 @@
       <c r="H70" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I70" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
         <v>80</v>
       </c>
@@ -2579,8 +2860,12 @@
       <c r="H71" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I71" s="7">
+        <f t="shared" si="1"/>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
         <v>81</v>
       </c>
@@ -2605,8 +2890,12 @@
       <c r="H72" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I72" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
         <v>82</v>
       </c>
@@ -2631,8 +2920,12 @@
       <c r="H73" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I73" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
         <v>83</v>
       </c>
@@ -2657,8 +2950,12 @@
       <c r="H74" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I74" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
         <v>84</v>
       </c>
@@ -2683,8 +2980,12 @@
       <c r="H75" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I75" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
         <v>85</v>
       </c>
@@ -2709,8 +3010,12 @@
       <c r="H76" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I76" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
         <v>86</v>
       </c>
@@ -2735,8 +3040,12 @@
       <c r="H77" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I77" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
         <v>87</v>
       </c>
@@ -2761,8 +3070,12 @@
       <c r="H78" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I78" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
         <v>88</v>
       </c>
@@ -2787,8 +3100,12 @@
       <c r="H79" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I79" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
         <v>89</v>
       </c>
@@ -2813,8 +3130,12 @@
       <c r="H80" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I80" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
         <v>90</v>
       </c>
@@ -2839,8 +3160,12 @@
       <c r="H81" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I81" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
         <v>91</v>
       </c>
@@ -2865,8 +3190,12 @@
       <c r="H82" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I82" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
         <v>92</v>
       </c>
@@ -2891,8 +3220,12 @@
       <c r="H83" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I83" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
         <v>93</v>
       </c>
@@ -2917,8 +3250,12 @@
       <c r="H84" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I84" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="s">
         <v>94</v>
       </c>
@@ -2943,8 +3280,12 @@
       <c r="H85" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I85" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
         <v>95</v>
       </c>
@@ -2969,8 +3310,12 @@
       <c r="H86" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I86" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
         <v>96</v>
       </c>
@@ -2995,8 +3340,12 @@
       <c r="H87" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I87" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
         <v>97</v>
       </c>
@@ -3021,8 +3370,12 @@
       <c r="H88" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I88" s="7">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
         <v>98</v>
       </c>
@@ -3047,8 +3400,12 @@
       <c r="H89" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I89" s="7">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
         <v>100</v>
       </c>
@@ -3073,8 +3430,12 @@
       <c r="H90" s="5" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I90" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>101</v>
       </c>
@@ -3099,8 +3460,13 @@
       <c r="H91" s="6" t="s">
         <v>10</v>
       </c>
+      <c r="I91" s="7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>